--- a/data/pack/ca/cerdo_ab.xlsx
+++ b/data/pack/ca/cerdo_ab.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5109,6 +5109,61 @@
         </is>
       </c>
       <c r="K85" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cerdo_ab</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cerdo en canal, precio al contado (Alberta)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2.041</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5212,7 +5267,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5278,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -5318,7 +5373,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>

--- a/data/pack/ca/cerdo_ab.xlsx
+++ b/data/pack/ca/cerdo_ab.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5164,6 +5164,61 @@
         </is>
       </c>
       <c r="K86" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cerdo_ab</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cerdo en canal, precio al contado (Alberta)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1.959</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5267,7 +5322,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5333,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -5373,7 +5428,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/data/pack/ca/cerdo_ab.xlsx
+++ b/data/pack/ca/cerdo_ab.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5219,6 +5219,61 @@
         </is>
       </c>
       <c r="K87" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cerdo_ab</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cerdo en canal, precio al contado (Alberta)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1.864</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5322,7 +5377,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5388,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -5428,7 +5483,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
